--- a/src/main/resources/reports/apk_17.xlsx
+++ b/src/main/resources/reports/apk_17.xlsx
@@ -461,16 +461,16 @@
     <t xml:space="preserve">171240</t>
   </si>
   <si>
-    <t xml:space="preserve">${fertilizerDispenser.atStartDateCount + sprayer.atStartDateCount}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${fertilizerDispenser.incomingCount + sprayer.incomingCount}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${fertilizerDispenser.decommissionedCount + sprayer.decommissionedCount}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${fertilizerDispenser.atEndDateCount + sprayer.atEndDateCount}</t>
+    <t xml:space="preserve">${fertilizer_dispenser.atStartDateCount + sprayer.atStartDateCount}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${fertilizer_dispenser.incomingCount + sprayer.incomingCount}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${fertilizer_dispenser.decommissionedCount + sprayer.decommissionedCount}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${fertilizer_dispenser.atEndDateCount + sprayer.atEndDateCount}</t>
   </si>
   <si>
     <t xml:space="preserve">машины сельскохозяйственные для обработки почвы прочие</t>
@@ -487,7 +487,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">${</t>
+      <t xml:space="preserve">${rolling_rinks</t>
     </r>
     <r>
       <rPr>
@@ -497,7 +497,7 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">rollingRinks.atStartDateCount</t>
+      <t xml:space="preserve">.atStartDateCount</t>
     </r>
     <r>
       <rPr>
@@ -519,7 +519,7 @@
         <family val="1"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">${</t>
+      <t xml:space="preserve">${rolling_rinks</t>
     </r>
     <r>
       <rPr>
@@ -529,7 +529,7 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">rollingRinks.</t>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -561,7 +561,7 @@
         <family val="1"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">${</t>
+      <t xml:space="preserve">${rolling_rinks</t>
     </r>
     <r>
       <rPr>
@@ -571,7 +571,7 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">rollingRinks.</t>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -603,7 +603,7 @@
         <family val="1"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">${</t>
+      <t xml:space="preserve">${rolling_rinks</t>
     </r>
     <r>
       <rPr>
@@ -613,7 +613,7 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">rollingRinks.</t>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -669,7 +669,7 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">hayHarvester.atStartDateCount</t>
+      <t xml:space="preserve">hay_harvester.atStartDateCount</t>
     </r>
     <r>
       <rPr>
@@ -691,7 +691,7 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">${hayHarvester.</t>
+      <t xml:space="preserve">${hay_harvester.</t>
     </r>
     <r>
       <rPr>
@@ -723,7 +723,7 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">${hayHarvester.</t>
+      <t xml:space="preserve">${hay_harvester.</t>
     </r>
     <r>
       <rPr>
@@ -755,7 +755,7 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">${hayHarvester.</t>
+      <t xml:space="preserve">${hay_harvester.</t>
     </r>
     <r>
       <rPr>
@@ -819,7 +819,7 @@
         <family val="1"/>
         <charset val="204"/>
       </rPr>
-      <t xml:space="preserve">${combine.</t>
+      <t xml:space="preserve">${combine_harvester.</t>
     </r>
     <r>
       <rPr>
@@ -851,7 +851,7 @@
         <family val="1"/>
         <charset val="204"/>
       </rPr>
-      <t xml:space="preserve">${combine.</t>
+      <t xml:space="preserve">${combine_harvester.</t>
     </r>
     <r>
       <rPr>
@@ -883,7 +883,7 @@
         <family val="1"/>
         <charset val="204"/>
       </rPr>
-      <t xml:space="preserve">${combine.</t>
+      <t xml:space="preserve">${combine_harvester.</t>
     </r>
     <r>
       <rPr>
@@ -915,7 +915,7 @@
         <family val="1"/>
         <charset val="204"/>
       </rPr>
-      <t xml:space="preserve">${combine.</t>
+      <t xml:space="preserve">${combine_harvester.</t>
     </r>
     <r>
       <rPr>
@@ -1314,7 +1314,7 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">irrigationSystem.atStartDateCount</t>
+      <t xml:space="preserve">irrigation_system.atStartDateCount</t>
     </r>
     <r>
       <rPr>
@@ -1338,7 +1338,7 @@
         <family val="1"/>
         <charset val="204"/>
       </rPr>
-      <t xml:space="preserve">${irrigationSystem</t>
+      <t xml:space="preserve">${irrigation_system</t>
     </r>
     <r>
       <rPr>
@@ -1383,7 +1383,7 @@
         <family val="1"/>
         <charset val="204"/>
       </rPr>
-      <t xml:space="preserve">${irrigationSystem</t>
+      <t xml:space="preserve">${irrigation_system</t>
     </r>
     <r>
       <rPr>
@@ -1407,7 +1407,7 @@
         <family val="1"/>
         <charset val="204"/>
       </rPr>
-      <t xml:space="preserve">${irrigationSystem</t>
+      <t xml:space="preserve">${irrigation_system</t>
     </r>
     <r>
       <rPr>
@@ -1480,8 +1480,8 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val=""/>
-        <family val="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">${</t>
@@ -1492,6 +1492,7 @@
         <color rgb="FF000000"/>
         <rFont val="JetBrains Mono"/>
         <family val="3"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">expense_current_period_</t>
     </r>
@@ -1499,8 +1500,8 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val=""/>
-        <family val="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">172130.totalAmount}</t>
@@ -1523,6 +1524,7 @@
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">totalAmount</t>
     </r>
@@ -1530,9 +1532,9 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val=""/>
-        <family val="1"/>
-        <charset val="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
       </rPr>
       <t xml:space="preserve">}</t>
     </r>
@@ -1555,8 +1557,8 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val=""/>
-        <family val="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">${</t>
@@ -1567,6 +1569,7 @@
         <color rgb="FF000000"/>
         <rFont val="JetBrains Mono"/>
         <family val="3"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">expense_current_period_</t>
     </r>
@@ -1574,8 +1577,8 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val=""/>
-        <family val="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">172141.</t>
@@ -1586,6 +1589,7 @@
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">totalAmount</t>
     </r>
@@ -1593,8 +1597,8 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val=""/>
-        <family val="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">}</t>
@@ -1617,18 +1621,9 @@
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">totalAmount</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val=""/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">totalAmount}</t>
     </r>
   </si>
   <si>
@@ -1661,8 +1656,8 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val=""/>
-        <family val="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">${</t>
@@ -1673,6 +1668,7 @@
         <color rgb="FF000000"/>
         <rFont val="JetBrains Mono"/>
         <family val="3"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">expense_current_period_</t>
     </r>
@@ -1680,8 +1676,8 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val=""/>
-        <family val="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">172151.</t>
@@ -1692,6 +1688,7 @@
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">totalAmount</t>
     </r>
@@ -1699,8 +1696,8 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val=""/>
-        <family val="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">}</t>
@@ -1723,45 +1720,36 @@
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">totalAmount</t>
-    </r>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">totalAmount}</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">172151.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172151.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Объем потребляемых нефтепродуктов всех видов - всего</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">тонн</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172161</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val=""/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">172151.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172151.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Объем потребляемых нефтепродуктов всех видов - всего</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">тонн</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172161</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val=""/>
-        <family val="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">${</t>
@@ -1772,6 +1760,7 @@
         <color rgb="FF000000"/>
         <rFont val="JetBrains Mono"/>
         <family val="3"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">expense_current_period_</t>
     </r>
@@ -1779,8 +1768,8 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val=""/>
-        <family val="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">172161.</t>
@@ -1791,6 +1780,7 @@
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">totalAmount</t>
     </r>
@@ -1798,8 +1788,8 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val=""/>
-        <family val="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">}</t>
@@ -1822,18 +1812,9 @@
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">totalAmount</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val=""/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">totalAmount}</t>
     </r>
   </si>
   <si>
@@ -1847,14 +1828,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="[=0]\-;General"/>
     <numFmt numFmtId="167" formatCode="@"/>
     <numFmt numFmtId="168" formatCode="0"/>
+    <numFmt numFmtId="169" formatCode="General"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1997,19 +1979,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val=""/>
-      <family val="1"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="JetBrains Mono"/>
-      <family val="3"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
@@ -2021,6 +1990,7 @@
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="5">
@@ -2390,19 +2360,19 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="23" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="21" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2422,15 +2392,15 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="4" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3016,23 +2986,23 @@
       </c>
       <c r="C19" s="37" t="str">
         <f aca="false">C20</f>
-        <v>${combine.atStartDateCount}</v>
+        <v>${combine_harvester.atStartDateCount}</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="38" t="str">
         <f aca="false">E20</f>
-        <v>${combine.incomingCount}</v>
+        <v>${combine_harvester.incomingCount}</v>
       </c>
       <c r="F19" s="15"/>
       <c r="G19" s="15"/>
       <c r="H19" s="38" t="str">
         <f aca="false">H20</f>
-        <v>${combine.decommissionedCount}</v>
+        <v>${combine_harvester.decommissionedCount}</v>
       </c>
       <c r="I19" s="15"/>
       <c r="J19" s="37" t="str">
         <f aca="false">J20</f>
-        <v>${combine.atEndDateCount}</v>
+        <v>${combine_harvester.atEndDateCount}</v>
       </c>
       <c r="K19" s="15"/>
       <c r="L19" s="17"/>
@@ -3385,7 +3355,7 @@
       <c r="K37" s="22"/>
       <c r="L37" s="25"/>
     </row>
-    <row r="38" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
         <v>132</v>
       </c>

--- a/src/main/resources/reports/apk_17.xlsx
+++ b/src/main/resources/reports/apk_17.xlsx
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="172">
   <si>
     <t xml:space="preserve">Наименование показателя</t>
   </si>
@@ -1449,9 +1449,6 @@
     <t xml:space="preserve">За отчетный год</t>
   </si>
   <si>
-    <t xml:space="preserve">За предыдущий год</t>
-  </si>
-  <si>
     <t xml:space="preserve">Всего энергетических мощностей</t>
   </si>
   <si>
@@ -1508,38 +1505,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve">${expense_previous_period_172130.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">totalAmount</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Отпущено электроэнергии (потреблено)</t>
   </si>
   <si>
@@ -1605,28 +1570,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">${expense_previous_period_172141.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">totalAmount}</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">из них: 
 на доработку, очистку и сушку</t>
   </si>
@@ -1704,28 +1647,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">${expense_previous_period_172151.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">totalAmount}</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">172151.1</t>
   </si>
   <si>
@@ -1793,28 +1714,6 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">}</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">${expense_previous_period_172161.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">totalAmount}</t>
     </r>
   </si>
   <si>
@@ -1836,7 +1735,7 @@
     <numFmt numFmtId="168" formatCode="0"/>
     <numFmt numFmtId="169" formatCode="General"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1974,26 +1873,13 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2002,20 +1888,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC5E0B4"/>
-        <bgColor rgb="FFAFD095"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFD095"/>
-        <bgColor rgb="FFC5E0B4"/>
       </patternFill>
     </fill>
   </fills>
@@ -2123,7 +1997,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="56">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2152,19 +2026,11 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2184,15 +2050,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2200,7 +2058,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="3" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2212,11 +2070,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2224,23 +2078,19 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2248,22 +2098,10 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2276,11 +2114,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2296,19 +2130,11 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2344,15 +2170,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2364,15 +2186,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="21" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2380,35 +2194,23 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="4" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2416,11 +2218,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2449,7 +2247,7 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFAFD095"/>
+      <rgbColor rgb="FFC0C0C0"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
@@ -2469,7 +2267,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFC5E0B4"/>
+      <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -2630,756 +2428,756 @@
         <f aca="false">E5</f>
         <v>${tractor.incomingCount}</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="9"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="7"/>
       <c r="H4" s="6" t="str">
         <f aca="false">H5</f>
         <v>${tractor.decommissionedCount}</v>
       </c>
-      <c r="I4" s="9"/>
+      <c r="I4" s="7"/>
       <c r="J4" s="6" t="str">
         <f aca="false">J5</f>
         <v>${tractor.atEndDateCount}</v>
       </c>
       <c r="K4" s="7"/>
-      <c r="L4" s="10"/>
-      <c r="N4" s="11"/>
+      <c r="L4" s="8"/>
+      <c r="N4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="14" t="s">
+      <c r="D5" s="12"/>
+      <c r="E5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="16"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="14" t="s">
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="15"/>
-      <c r="J5" s="14" t="s">
+      <c r="I5" s="12"/>
+      <c r="J5" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="K5" s="15"/>
-      <c r="L5" s="17"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="17"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="17"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="57" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="21" t="n">
+      <c r="C8" s="17" t="n">
         <f aca="false">SUM(C9:C13)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="22"/>
-      <c r="E8" s="21" t="n">
+      <c r="D8" s="18"/>
+      <c r="E8" s="17" t="n">
         <f aca="false">SUM(E9:E13)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="23"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="24" t="n">
+      <c r="F8" s="17"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="19" t="n">
         <f aca="false">SUM(H9:H13)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="22"/>
-      <c r="J8" s="21" t="n">
+      <c r="I8" s="18"/>
+      <c r="J8" s="17" t="n">
         <f aca="false">SUM(J9:J13)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="22"/>
-      <c r="L8" s="25"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="20"/>
     </row>
     <row r="9" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="26" t="s">
+      <c r="D9" s="12"/>
+      <c r="E9" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="27" t="s">
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="I9" s="15"/>
-      <c r="J9" s="14" t="s">
+      <c r="I9" s="12"/>
+      <c r="J9" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="K9" s="15"/>
-      <c r="L9" s="17"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="14" t="s">
+      <c r="D10" s="12"/>
+      <c r="E10" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="F10" s="28"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="29" t="s">
+      <c r="F10" s="22"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="I10" s="15"/>
-      <c r="J10" s="14" t="s">
+      <c r="I10" s="12"/>
+      <c r="J10" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="K10" s="15"/>
-      <c r="L10" s="17"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="26" t="s">
+      <c r="D11" s="12"/>
+      <c r="E11" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="26" t="s">
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="I11" s="15"/>
-      <c r="J11" s="14" t="s">
+      <c r="I11" s="12"/>
+      <c r="J11" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="K11" s="15"/>
-      <c r="L11" s="17"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="26" t="s">
+      <c r="D12" s="12"/>
+      <c r="E12" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="26" t="s">
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="I12" s="15"/>
-      <c r="J12" s="14" t="s">
+      <c r="I12" s="12"/>
+      <c r="J12" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="K12" s="15"/>
-      <c r="L12" s="17"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="33.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="31" t="s">
+      <c r="D13" s="12"/>
+      <c r="E13" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="31" t="s">
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="I13" s="15"/>
-      <c r="J13" s="32" t="s">
+      <c r="I13" s="12"/>
+      <c r="J13" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="K13" s="15"/>
-      <c r="L13" s="17"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="13"/>
     </row>
     <row r="14" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="21" t="e">
+      <c r="C14" s="17" t="e">
         <f aca="false">C15+C19</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="33" t="e">
+      <c r="D14" s="18"/>
+      <c r="E14" s="18" t="e">
         <f aca="false">E15+E19</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="33" t="e">
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18" t="e">
         <f aca="false">H15+H19</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I14" s="22"/>
-      <c r="J14" s="21" t="e">
+      <c r="I14" s="18"/>
+      <c r="J14" s="17" t="e">
         <f aca="false">J15+J19</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K14" s="22"/>
-      <c r="L14" s="25"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="C15" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="34" t="s">
+      <c r="D15" s="12"/>
+      <c r="E15" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="34" t="s">
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="I15" s="15"/>
-      <c r="J15" s="35" t="s">
+      <c r="I15" s="12"/>
+      <c r="J15" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="K15" s="15"/>
-      <c r="L15" s="17"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="13"/>
     </row>
     <row r="16" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="36" t="s">
+      <c r="A16" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="17"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="17"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="17"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C19" s="37" t="str">
+      <c r="C19" s="28" t="str">
         <f aca="false">C20</f>
         <v>${combine_harvester.atStartDateCount}</v>
       </c>
-      <c r="D19" s="15"/>
-      <c r="E19" s="38" t="str">
+      <c r="D19" s="12"/>
+      <c r="E19" s="29" t="str">
         <f aca="false">E20</f>
         <v>${combine_harvester.incomingCount}</v>
       </c>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="38" t="str">
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="29" t="str">
         <f aca="false">H20</f>
         <v>${combine_harvester.decommissionedCount}</v>
       </c>
-      <c r="I19" s="15"/>
-      <c r="J19" s="37" t="str">
+      <c r="I19" s="12"/>
+      <c r="J19" s="28" t="str">
         <f aca="false">J20</f>
         <v>${combine_harvester.atEndDateCount}</v>
       </c>
-      <c r="K19" s="15"/>
-      <c r="L19" s="17"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="13"/>
     </row>
     <row r="20" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="36" t="s">
+      <c r="A20" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="D20" s="15"/>
-      <c r="E20" s="26" t="s">
+      <c r="D20" s="12"/>
+      <c r="E20" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="26" t="s">
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="I20" s="15"/>
-      <c r="J20" s="14" t="s">
+      <c r="I20" s="12"/>
+      <c r="J20" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="K20" s="15"/>
-      <c r="L20" s="17"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="36" t="s">
+      <c r="A21" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="17"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="13"/>
     </row>
     <row r="22" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="17"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="13"/>
     </row>
     <row r="23" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="17"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="13"/>
     </row>
     <row r="24" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="15"/>
-      <c r="L24" s="17"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="13"/>
     </row>
     <row r="25" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="17"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="17"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="13"/>
     </row>
     <row r="27" customFormat="false" ht="57" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B27" s="20" t="s">
+      <c r="B27" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="22"/>
-      <c r="L27" s="25"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="20"/>
     </row>
     <row r="28" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="17"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="13"/>
     </row>
     <row r="29" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="17"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="36" t="s">
+      <c r="A30" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="17"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="13"/>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="17"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="17"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="13"/>
     </row>
     <row r="33" customFormat="false" ht="57" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="12" t="s">
+      <c r="A33" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
-      <c r="K33" s="15"/>
-      <c r="L33" s="17"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="13"/>
     </row>
     <row r="34" customFormat="false" ht="57" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B34" s="20" t="s">
+      <c r="B34" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="22"/>
-      <c r="J34" s="22"/>
-      <c r="K34" s="22"/>
-      <c r="L34" s="25"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18"/>
+      <c r="J34" s="18"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="20"/>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B35" s="20" t="s">
+      <c r="B35" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C35" s="39" t="s">
+      <c r="C35" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="D35" s="22"/>
-      <c r="E35" s="33" t="s">
+      <c r="D35" s="18"/>
+      <c r="E35" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="33" t="s">
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="I35" s="22"/>
-      <c r="J35" s="39" t="s">
+      <c r="I35" s="18"/>
+      <c r="J35" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="K35" s="22"/>
-      <c r="L35" s="25"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="20"/>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B36" s="20" t="s">
+      <c r="B36" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="C36" s="22"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="22"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="22"/>
-      <c r="I36" s="22"/>
-      <c r="J36" s="22"/>
-      <c r="K36" s="22"/>
-      <c r="L36" s="25"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="18"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="20"/>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="40" t="s">
+      <c r="A37" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="B37" s="20" t="s">
+      <c r="B37" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="C37" s="39" t="s">
+      <c r="C37" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="D37" s="22"/>
-      <c r="E37" s="33" t="s">
+      <c r="D37" s="18"/>
+      <c r="E37" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="F37" s="22"/>
-      <c r="G37" s="22"/>
-      <c r="H37" s="33" t="s">
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="I37" s="22"/>
-      <c r="J37" s="39" t="s">
+      <c r="I37" s="18"/>
+      <c r="J37" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="K37" s="22"/>
-      <c r="L37" s="25"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="20"/>
     </row>
     <row r="38" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B38" s="41" t="s">
+      <c r="B38" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="C38" s="42" t="s">
+      <c r="C38" s="32" t="s">
         <v>134</v>
       </c>
-      <c r="D38" s="43"/>
-      <c r="E38" s="44" t="s">
+      <c r="D38" s="33"/>
+      <c r="E38" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="F38" s="43"/>
-      <c r="G38" s="43"/>
-      <c r="H38" s="44" t="s">
+      <c r="F38" s="33"/>
+      <c r="G38" s="33"/>
+      <c r="H38" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="I38" s="43"/>
-      <c r="J38" s="45" t="s">
+      <c r="I38" s="33"/>
+      <c r="J38" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="K38" s="43"/>
-      <c r="L38" s="46"/>
+      <c r="K38" s="33"/>
+      <c r="L38" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -3406,7 +3204,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="47.62"/>
@@ -3416,268 +3214,230 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="6" style="0" width="11.25"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="47" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="C1" s="37" t="s">
         <v>138</v>
       </c>
-      <c r="D1" s="49" t="s">
+      <c r="D1" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="E1" s="49" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="38" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="39" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="50" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="50" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="51" t="s">
+      <c r="B3" s="40" t="s">
         <v>141</v>
       </c>
-      <c r="B3" s="52" t="s">
+      <c r="C3" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="D3" s="42"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="39" t="s">
         <v>143</v>
       </c>
-      <c r="D3" s="54"/>
-      <c r="E3" s="55"/>
-    </row>
-    <row r="4" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="51" t="s">
+      <c r="B4" s="43" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="56" t="s">
+      <c r="C4" s="37" t="s">
         <v>145</v>
       </c>
-      <c r="C4" s="49" t="s">
+      <c r="D4" s="44"/>
+    </row>
+    <row r="5" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="D4" s="47"/>
-      <c r="E4" s="57"/>
-    </row>
-    <row r="5" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="58" t="s">
+      <c r="B5" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="B5" s="56" t="s">
+      <c r="C5" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="D5" s="46" t="s">
         <v>148</v>
       </c>
-      <c r="C5" s="49" t="s">
-        <v>146</v>
-      </c>
-      <c r="D5" s="59" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="39" t="s">
         <v>149</v>
       </c>
-      <c r="E5" s="60" t="s">
+      <c r="B6" s="43" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="51" t="s">
-        <v>151</v>
-      </c>
-      <c r="B6" s="56" t="s">
-        <v>152</v>
-      </c>
-      <c r="C6" s="49" t="s">
-        <v>146</v>
-      </c>
-      <c r="D6" s="61" t="str">
+      <c r="C6" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="D6" s="47" t="str">
         <f aca="false">D7</f>
         <v>${expense_current_period_172141.totalAmount}</v>
       </c>
-      <c r="E6" s="62" t="str">
-        <f aca="false">E7</f>
-        <v>${expense_previous_period_172141.totalAmount}</v>
-      </c>
     </row>
     <row r="7" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="63" t="s">
+      <c r="A7" s="48" t="s">
+        <v>151</v>
+      </c>
+      <c r="B7" s="49" t="s">
+        <v>152</v>
+      </c>
+      <c r="C7" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="D7" s="46" t="s">
         <v>153</v>
       </c>
-      <c r="B7" s="64" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="50" t="s">
         <v>154</v>
       </c>
-      <c r="C7" s="49" t="s">
-        <v>146</v>
-      </c>
-      <c r="D7" s="59" t="s">
+      <c r="B8" s="49" t="s">
         <v>155</v>
       </c>
-      <c r="E7" s="65" t="s">
+      <c r="C8" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="D8" s="51"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="50" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="27" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="66" t="s">
+      <c r="B9" s="49" t="s">
         <v>157</v>
       </c>
-      <c r="B8" s="64" t="s">
+      <c r="C9" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="D9" s="51"/>
+    </row>
+    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="39" t="s">
         <v>158</v>
       </c>
-      <c r="C8" s="49" t="s">
-        <v>146</v>
-      </c>
-      <c r="D8" s="67"/>
-      <c r="E8" s="68"/>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="66" t="s">
+      <c r="B10" s="49" t="s">
         <v>159</v>
       </c>
-      <c r="B9" s="64" t="s">
+      <c r="C10" s="37" t="s">
         <v>160</v>
       </c>
-      <c r="C9" s="49" t="s">
-        <v>146</v>
-      </c>
-      <c r="D9" s="67"/>
-      <c r="E9" s="68"/>
-    </row>
-    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="51" t="s">
-        <v>161</v>
-      </c>
-      <c r="B10" s="64" t="s">
-        <v>162</v>
-      </c>
-      <c r="C10" s="49" t="s">
-        <v>163</v>
-      </c>
-      <c r="D10" s="69" t="str">
+      <c r="D10" s="52" t="str">
         <f aca="false">D11</f>
         <v>${expense_current_period_172151.totalAmount}</v>
       </c>
-      <c r="E10" s="62" t="str">
-        <f aca="false">E11</f>
-        <v>${expense_previous_period_172151.totalAmount}</v>
-      </c>
     </row>
     <row r="11" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="63" t="s">
-        <v>153</v>
-      </c>
-      <c r="B11" s="64" t="s">
+      <c r="A11" s="48" t="s">
+        <v>151</v>
+      </c>
+      <c r="B11" s="49" t="s">
+        <v>161</v>
+      </c>
+      <c r="C11" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="D11" s="46" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="50" t="s">
+        <v>154</v>
+      </c>
+      <c r="B12" s="49" t="s">
+        <v>163</v>
+      </c>
+      <c r="C12" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="D12" s="51"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="50" t="s">
+        <v>156</v>
+      </c>
+      <c r="B13" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="C11" s="49" t="s">
-        <v>163</v>
-      </c>
-      <c r="D11" s="59" t="s">
+      <c r="C13" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="D13" s="51"/>
+    </row>
+    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="39" t="s">
         <v>165</v>
       </c>
-      <c r="E11" s="65" t="s">
+      <c r="B14" s="49" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="27" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="66" t="s">
-        <v>157</v>
-      </c>
-      <c r="B12" s="64" t="s">
+      <c r="C14" s="37" t="s">
         <v>167</v>
       </c>
-      <c r="C12" s="49" t="s">
-        <v>163</v>
-      </c>
-      <c r="D12" s="67"/>
-      <c r="E12" s="68"/>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="66" t="s">
-        <v>159</v>
-      </c>
-      <c r="B13" s="64" t="s">
-        <v>168</v>
-      </c>
-      <c r="C13" s="49" t="s">
-        <v>163</v>
-      </c>
-      <c r="D13" s="67"/>
-      <c r="E13" s="68"/>
-    </row>
-    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="51" t="s">
-        <v>169</v>
-      </c>
-      <c r="B14" s="64" t="s">
-        <v>170</v>
-      </c>
-      <c r="C14" s="49" t="s">
-        <v>171</v>
-      </c>
-      <c r="D14" s="69" t="str">
+      <c r="D14" s="52" t="str">
         <f aca="false">D15</f>
         <v>${expense_current_period_172161.totalAmount}</v>
       </c>
-      <c r="E14" s="62" t="str">
-        <f aca="false">E15</f>
-        <v>${expense_previous_period_172161.totalAmount}</v>
-      </c>
     </row>
     <row r="15" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="63" t="s">
-        <v>153</v>
-      </c>
-      <c r="B15" s="64" t="s">
-        <v>172</v>
-      </c>
-      <c r="C15" s="49" t="s">
+      <c r="A15" s="48" t="s">
+        <v>151</v>
+      </c>
+      <c r="B15" s="49" t="s">
+        <v>168</v>
+      </c>
+      <c r="C15" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="D15" s="46" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="50" t="s">
+        <v>154</v>
+      </c>
+      <c r="B16" s="49" t="s">
+        <v>170</v>
+      </c>
+      <c r="C16" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="D16" s="44"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="50" t="s">
+        <v>156</v>
+      </c>
+      <c r="B17" s="53" t="s">
         <v>171</v>
       </c>
-      <c r="D15" s="59" t="s">
-        <v>173</v>
-      </c>
-      <c r="E15" s="65" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="27" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="66" t="s">
-        <v>157</v>
-      </c>
-      <c r="B16" s="64" t="s">
-        <v>175</v>
-      </c>
-      <c r="C16" s="49" t="s">
-        <v>171</v>
-      </c>
-      <c r="D16" s="47"/>
-      <c r="E16" s="70"/>
-    </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="66" t="s">
-        <v>159</v>
-      </c>
-      <c r="B17" s="71" t="s">
-        <v>176</v>
-      </c>
-      <c r="C17" s="72" t="s">
-        <v>171</v>
-      </c>
-      <c r="D17" s="73"/>
-      <c r="E17" s="74"/>
+      <c r="C17" s="54" t="s">
+        <v>167</v>
+      </c>
+      <c r="D17" s="55"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
